--- a/projetPFA/outputs/test_Machines_Test.xlsx
+++ b/projetPFA/outputs/test_Machines_Test.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Lignes_utiles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lignes_rejetees" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +471,7 @@
         <v>14.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +523,7 @@
         <v>6.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.955</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +549,7 @@
         <v>4.38</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +575,7 @@
         <v>7.84</v>
       </c>
       <c r="F6" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +601,7 @@
         <v>11.57</v>
       </c>
       <c r="F7" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="8">
@@ -654,7 +653,7 @@
         <v>7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +679,7 @@
         <v>9.35</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="11">
@@ -706,7 +705,7 @@
         <v>6.41</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +757,7 @@
         <v>7.71</v>
       </c>
       <c r="F13" t="n">
-        <v>0.755</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +783,7 @@
         <v>4.07</v>
       </c>
       <c r="F14" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +809,7 @@
         <v>0.52</v>
       </c>
       <c r="F15" t="n">
-        <v>0.975</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -836,7 +835,7 @@
         <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="17">
@@ -862,7 +861,7 @@
         <v>8.98</v>
       </c>
       <c r="F17" t="n">
-        <v>0.915</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="18">
@@ -888,7 +887,7 @@
         <v>10.26</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="19">
@@ -914,7 +913,7 @@
         <v>1.11</v>
       </c>
       <c r="F19" t="n">
-        <v>0.945</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +939,7 @@
         <v>8.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.985</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +965,7 @@
         <v>14.54</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="22">
@@ -992,7 +991,7 @@
         <v>6.16</v>
       </c>
       <c r="F22" t="n">
-        <v>0.985</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,7 +1017,7 @@
         <v>8.140000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24">
@@ -1044,7 +1043,7 @@
         <v>13.95</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="25">
@@ -1070,7 +1069,7 @@
         <v>12.95</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="26">
@@ -1096,7 +1095,7 @@
         <v>11.33</v>
       </c>
       <c r="F26" t="n">
-        <v>0.995</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="27">
@@ -1122,7 +1121,7 @@
         <v>4.37</v>
       </c>
       <c r="F27" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="28">
@@ -1148,7 +1147,7 @@
         <v>12.23</v>
       </c>
       <c r="F28" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="29">
@@ -1174,7 +1173,7 @@
         <v>7.08</v>
       </c>
       <c r="F29" t="n">
-        <v>0.835</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="30">
@@ -1200,7 +1199,7 @@
         <v>1.33</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="31">
@@ -1226,7 +1225,7 @@
         <v>2.73</v>
       </c>
       <c r="F31" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1252,7 +1251,7 @@
         <v>5.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33">
@@ -1278,7 +1277,7 @@
         <v>10.98</v>
       </c>
       <c r="F33" t="n">
-        <v>0.985</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="34">
@@ -1304,7 +1303,7 @@
         <v>2.75</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="35">
@@ -1330,7 +1329,7 @@
         <v>4.66</v>
       </c>
       <c r="F35" t="n">
-        <v>0.985</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36">
@@ -1356,7 +1355,7 @@
         <v>12.12</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="37">
@@ -1382,7 +1381,7 @@
         <v>11.41</v>
       </c>
       <c r="F37" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1408,7 +1407,7 @@
         <v>6.48</v>
       </c>
       <c r="F38" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="39">
@@ -1434,7 +1433,7 @@
         <v>12.06</v>
       </c>
       <c r="F39" t="n">
-        <v>0.985</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="40">
@@ -1460,7 +1459,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="41">
@@ -1486,7 +1485,7 @@
         <v>4.21</v>
       </c>
       <c r="F41" t="n">
-        <v>0.96</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="42">
@@ -1512,7 +1511,7 @@
         <v>4.88</v>
       </c>
       <c r="F42" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="43">
@@ -1564,7 +1563,7 @@
         <v>13.64</v>
       </c>
       <c r="F44" t="n">
-        <v>0.985</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="45">
@@ -1590,7 +1589,7 @@
         <v>12.99</v>
       </c>
       <c r="F45" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="46">
@@ -1616,7 +1615,7 @@
         <v>12.11</v>
       </c>
       <c r="F46" t="n">
-        <v>0.985</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1642,7 +1641,7 @@
         <v>2.94</v>
       </c>
       <c r="F47" t="n">
-        <v>0.995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="48">
@@ -1694,275 +1693,7 @@
         <v>7.63</v>
       </c>
       <c r="F49" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>HeuresFonctionnement</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TauxDefaut_%</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>utilite_predite</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score_confiance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Optimel Ferite_738720</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Testeur fonctionnel_518801</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Station de vissage_191161</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>E-Test Leshin_624902</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Station de vissage_308496</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Convoyeur_559381</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Convoyeur_322955</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3854.25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
